--- a/artfynd/A 18716-2024 artfynd.xlsx
+++ b/artfynd/A 18716-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753399</v>
+        <v>117753394</v>
       </c>
       <c r="B2" t="n">
         <v>57287</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422043</v>
+        <v>422009</v>
       </c>
       <c r="R2" t="n">
-        <v>7052893</v>
+        <v>7052826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117753459</v>
+        <v>117753399</v>
       </c>
       <c r="B3" t="n">
-        <v>86816</v>
+        <v>57287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422044</v>
+        <v>422043</v>
       </c>
       <c r="R3" t="n">
-        <v>7052895</v>
+        <v>7052893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753401</v>
+        <v>117753389</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422063</v>
+        <v>421987</v>
       </c>
       <c r="R4" t="n">
-        <v>7052931</v>
+        <v>7052893</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753451</v>
+        <v>117753388</v>
       </c>
       <c r="B5" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422022</v>
+        <v>422000</v>
       </c>
       <c r="R5" t="n">
-        <v>7052898</v>
+        <v>7052893</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753404</v>
+        <v>117753392</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422046</v>
+        <v>422004</v>
       </c>
       <c r="R6" t="n">
-        <v>7052944</v>
+        <v>7052861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753400</v>
+        <v>117753397</v>
       </c>
       <c r="B7" t="n">
         <v>57287</v>
@@ -1240,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422050</v>
+        <v>422019</v>
       </c>
       <c r="R7" t="n">
-        <v>7052899</v>
+        <v>7052871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753392</v>
+        <v>117753459</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>86816</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422004</v>
+        <v>422044</v>
       </c>
       <c r="R8" t="n">
-        <v>7052861</v>
+        <v>7052895</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753396</v>
+        <v>117753400</v>
       </c>
       <c r="B9" t="n">
         <v>57287</v>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422031</v>
+        <v>422050</v>
       </c>
       <c r="R9" t="n">
-        <v>7052864</v>
+        <v>7052899</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117753391</v>
+        <v>117753398</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421985</v>
+        <v>422023</v>
       </c>
       <c r="R10" t="n">
-        <v>7052888</v>
+        <v>7052870</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117753397</v>
+        <v>117753403</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422019</v>
+        <v>422054</v>
       </c>
       <c r="R11" t="n">
-        <v>7052871</v>
+        <v>7052934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753402</v>
+        <v>117753404</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1775,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>422075</v>
+        <v>422046</v>
       </c>
       <c r="R12" t="n">
-        <v>7052951</v>
+        <v>7052944</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117753394</v>
+        <v>117753396</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -1882,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>422009</v>
+        <v>422031</v>
       </c>
       <c r="R13" t="n">
-        <v>7052826</v>
+        <v>7052864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117753389</v>
+        <v>117753402</v>
       </c>
       <c r="B14" t="n">
         <v>57287</v>
@@ -1989,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421987</v>
+        <v>422075</v>
       </c>
       <c r="R14" t="n">
-        <v>7052893</v>
+        <v>7052951</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117753388</v>
+        <v>117753391</v>
       </c>
       <c r="B16" t="n">
         <v>57287</v>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>422000</v>
+        <v>421985</v>
       </c>
       <c r="R16" t="n">
-        <v>7052893</v>
+        <v>7052888</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2248,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117753398</v>
+        <v>117753401</v>
       </c>
       <c r="B17" t="n">
         <v>57287</v>
@@ -2310,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>422023</v>
+        <v>422063</v>
       </c>
       <c r="R17" t="n">
-        <v>7052870</v>
+        <v>7052931</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117753403</v>
+        <v>117753451</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>422054</v>
+        <v>422022</v>
       </c>
       <c r="R18" t="n">
-        <v>7052934</v>
+        <v>7052898</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,11 +2458,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 18716-2024 artfynd.xlsx
+++ b/artfynd/A 18716-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117753394</v>
+        <v>117753403</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422009</v>
+        <v>422054</v>
       </c>
       <c r="R2" t="n">
-        <v>7052826</v>
+        <v>7052934</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117753399</v>
+        <v>117753391</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422043</v>
+        <v>421985</v>
       </c>
       <c r="R3" t="n">
-        <v>7052893</v>
+        <v>7052888</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117753389</v>
+        <v>117753396</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421987</v>
+        <v>422031</v>
       </c>
       <c r="R4" t="n">
-        <v>7052893</v>
+        <v>7052864</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117753388</v>
+        <v>117753399</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422000</v>
+        <v>422043</v>
       </c>
       <c r="R5" t="n">
         <v>7052893</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117753392</v>
+        <v>117753397</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422004</v>
+        <v>422019</v>
       </c>
       <c r="R6" t="n">
-        <v>7052861</v>
+        <v>7052871</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117753397</v>
+        <v>117753400</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422019</v>
+        <v>422050</v>
       </c>
       <c r="R7" t="n">
-        <v>7052871</v>
+        <v>7052899</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117753459</v>
+        <v>117753392</v>
       </c>
       <c r="B8" t="n">
-        <v>86816</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422044</v>
+        <v>422004</v>
       </c>
       <c r="R8" t="n">
-        <v>7052895</v>
+        <v>7052861</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117753400</v>
+        <v>117753395</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422050</v>
+        <v>422031</v>
       </c>
       <c r="R9" t="n">
-        <v>7052899</v>
+        <v>7052825</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,7 +1534,7 @@
         <v>117753398</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117753403</v>
+        <v>117753402</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422054</v>
+        <v>422075</v>
       </c>
       <c r="R11" t="n">
-        <v>7052934</v>
+        <v>7052951</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753404</v>
+        <v>117753401</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>422046</v>
+        <v>422063</v>
       </c>
       <c r="R12" t="n">
-        <v>7052944</v>
+        <v>7052931</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117753396</v>
+        <v>117753451</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,21 +1868,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>422031</v>
+        <v>422022</v>
       </c>
       <c r="R13" t="n">
-        <v>7052864</v>
+        <v>7052898</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,11 +1928,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1954,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117753402</v>
+        <v>117753404</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>422075</v>
+        <v>422046</v>
       </c>
       <c r="R14" t="n">
-        <v>7052951</v>
+        <v>7052944</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117753395</v>
+        <v>117753394</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>422031</v>
+        <v>422009</v>
       </c>
       <c r="R15" t="n">
-        <v>7052825</v>
+        <v>7052826</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117753391</v>
+        <v>117753459</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>86818</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421985</v>
+        <v>422044</v>
       </c>
       <c r="R16" t="n">
-        <v>7052888</v>
+        <v>7052895</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,11 +2244,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117753401</v>
+        <v>117753388</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>422063</v>
+        <v>422000</v>
       </c>
       <c r="R17" t="n">
-        <v>7052931</v>
+        <v>7052893</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117753451</v>
+        <v>117753389</v>
       </c>
       <c r="B18" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2393,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>422022</v>
+        <v>421987</v>
       </c>
       <c r="R18" t="n">
-        <v>7052898</v>
+        <v>7052893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,6 +2453,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
